--- a/Budgeting System_Manpower Report.xlsx
+++ b/Budgeting System_Manpower Report.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oclpholdings-my.sharepoint.com/personal/jumalonpvp_ortigas_com_ph/Documents/Documents/Budgeting System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="410" documentId="8_{B440BBE7-9F96-47D5-8577-254065B29B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BCFEA10-B06C-4FE9-A53E-7B26210EFED9}"/>
+  <xr:revisionPtr revIDLastSave="465" documentId="8_{B440BBE7-9F96-47D5-8577-254065B29B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2C1DDFC-A472-40A7-AEEA-1EEB5FE00D9D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{09E9E6D6-0F48-4124-9B86-4777CBE4DCA7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{09E9E6D6-0F48-4124-9B86-4777CBE4DCA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel Report2" sheetId="5" state="hidden" r:id="rId1"/>
-    <sheet name="Dashboard Report" sheetId="4" r:id="rId2"/>
-    <sheet name="Excel Report" sheetId="1" r:id="rId3"/>
+    <sheet name="Manpower Budget Report" sheetId="4" r:id="rId2"/>
+    <sheet name="Manpower Budget Detailed Report" sheetId="6" r:id="rId3"/>
+    <sheet name="Excel Report" sheetId="1" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Excel Report'!$A$3:$BU$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Excel Report'!$A$3:$BU$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -89,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="54">
   <si>
     <t>OCC</t>
   </si>
@@ -242,6 +243,15 @@
   </si>
   <si>
     <t xml:space="preserve">Total Salary </t>
+  </si>
+  <si>
+    <t>Total Other Employee Benefits</t>
+  </si>
+  <si>
+    <t>from Standard Request</t>
+  </si>
+  <si>
+    <t>N/A - should be Zero</t>
   </si>
 </sst>
 </file>
@@ -422,7 +432,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -517,6 +527,12 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1392,7 +1408,537 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D18095FC-A571-4BBD-956B-9C9085559C95}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="44.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="25.26953125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="25.453125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6328125" customWidth="1"/>
+    <col min="8" max="9" width="29.6328125" customWidth="1"/>
+    <col min="10" max="10" width="14.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" s="42" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="B2" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5">
+        <v>258377600</v>
+      </c>
+      <c r="C5" s="5">
+        <v>258377600</v>
+      </c>
+      <c r="D5" s="5">
+        <f>B5+C5</f>
+        <v>516755200</v>
+      </c>
+      <c r="E5" s="6">
+        <f>D5*0.06</f>
+        <v>31005312</v>
+      </c>
+      <c r="F5" s="6">
+        <v>4183536</v>
+      </c>
+      <c r="G5" s="7">
+        <f>D5+E5+F5</f>
+        <v>551944048</v>
+      </c>
+      <c r="H5" s="46">
+        <f>G5-D5</f>
+        <v>35188848</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" ref="I5:I10" si="0">IFERROR(H5/D5,)</f>
+        <v>6.8095779200673737E-2</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="5">
+        <v>55434396</v>
+      </c>
+      <c r="C6" s="5">
+        <v>55434396</v>
+      </c>
+      <c r="D6" s="5">
+        <f>B6+C6</f>
+        <v>110868792</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="shared" ref="E6" si="1">D6*0.06</f>
+        <v>6652127.5199999996</v>
+      </c>
+      <c r="F6" s="6">
+        <v>347256</v>
+      </c>
+      <c r="G6" s="7">
+        <f t="shared" ref="G6:G9" si="2">D6+E6+F6</f>
+        <v>117868175.52</v>
+      </c>
+      <c r="H6" s="46">
+        <f t="shared" ref="H6:H9" si="3">G6-D6</f>
+        <v>6999383.5199999958</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="0"/>
+        <v>6.3132134785052904E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5">
+        <v>13229374.523517389</v>
+      </c>
+      <c r="C7" s="5">
+        <v>13229374.523517389</v>
+      </c>
+      <c r="D7" s="5">
+        <f>B7+C7</f>
+        <v>26458749.047034778</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>169440</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="2"/>
+        <v>26628189.047034778</v>
+      </c>
+      <c r="H7" s="46">
+        <f t="shared" si="3"/>
+        <v>169440</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="0"/>
+        <v>6.403930877411949E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="5">
+        <v>740654.86782760639</v>
+      </c>
+      <c r="C8" s="5">
+        <v>740654.86782760639</v>
+      </c>
+      <c r="D8" s="5">
+        <f>B8+C8</f>
+        <v>1481309.7356552128</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>9600</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" si="2"/>
+        <v>1490909.7356552128</v>
+      </c>
+      <c r="H8" s="46">
+        <f t="shared" si="3"/>
+        <v>9600</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="0"/>
+        <v>6.4807513033415184E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="8">
+        <v>4526723.9400540851</v>
+      </c>
+      <c r="C9" s="8">
+        <v>4526723.9400540851</v>
+      </c>
+      <c r="D9" s="8">
+        <f>B9+C9</f>
+        <v>9053447.8801081702</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9">
+        <v>52088.400000000009</v>
+      </c>
+      <c r="G9" s="14">
+        <f t="shared" si="2"/>
+        <v>9105536.2801081706</v>
+      </c>
+      <c r="H9" s="47">
+        <f t="shared" si="3"/>
+        <v>52088.400000000373</v>
+      </c>
+      <c r="I9" s="11">
+        <f t="shared" si="0"/>
+        <v>5.7534323596700292E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="48">
+        <f>SUM(B5:B9)</f>
+        <v>332308749.33139902</v>
+      </c>
+      <c r="C10" s="48">
+        <f t="shared" ref="C10:H10" si="4">SUM(C5:C9)</f>
+        <v>332308749.33139902</v>
+      </c>
+      <c r="D10" s="48">
+        <f t="shared" si="4"/>
+        <v>664617498.66279805</v>
+      </c>
+      <c r="E10" s="48">
+        <f t="shared" si="4"/>
+        <v>37657439.519999996</v>
+      </c>
+      <c r="F10" s="48">
+        <f t="shared" si="4"/>
+        <v>4761920.4000000004</v>
+      </c>
+      <c r="G10" s="48">
+        <f t="shared" si="4"/>
+        <v>707036858.58279812</v>
+      </c>
+      <c r="H10" s="48">
+        <f t="shared" si="4"/>
+        <v>42419359.919999994</v>
+      </c>
+      <c r="I10" s="49">
+        <f t="shared" si="0"/>
+        <v>6.3825222786560998E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="B12" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="1">
+        <f>IFERROR(H14/D14,)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" ref="I15:I29" si="5">IFERROR(H15/D15,)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="37"/>
+      <c r="I18" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="38"/>
+      <c r="I19" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="51"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="53">
+        <f>SUM(B14:B28)</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="53">
+        <f t="shared" ref="C29:H29" si="6">SUM(C14:C28)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="49">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC8252AF-3106-4BEF-8A24-2B5D61C2AD23}">
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.90625" bestFit="1" customWidth="1"/>
@@ -1498,7 +2044,7 @@
         <v>35188848</v>
       </c>
       <c r="I5" s="1">
-        <f>H5/D5</f>
+        <f t="shared" ref="I5:I10" si="0">IFERROR(H5/D5,)</f>
         <v>6.8095779200673737E-2</v>
       </c>
       <c r="J5" s="2"/>
@@ -1514,26 +2060,26 @@
         <v>55434396</v>
       </c>
       <c r="D6" s="5">
-        <f t="shared" ref="D6:D9" si="0">B6+C6</f>
+        <f t="shared" ref="D6:D9" si="1">B6+C6</f>
         <v>110868792</v>
       </c>
       <c r="E6" s="6">
-        <f t="shared" ref="E6" si="1">D6*0.06</f>
+        <f t="shared" ref="E6" si="2">D6*0.06</f>
         <v>6652127.5199999996</v>
       </c>
       <c r="F6" s="6">
         <v>347256</v>
       </c>
       <c r="G6" s="7">
-        <f t="shared" ref="G6:G9" si="2">D6+E6+F6</f>
+        <f t="shared" ref="G6:G9" si="3">D6+E6+F6</f>
         <v>117868175.52</v>
       </c>
       <c r="H6" s="46">
-        <f t="shared" ref="H6:H9" si="3">G6-D6</f>
+        <f t="shared" ref="H6:H9" si="4">G6-D6</f>
         <v>6999383.5199999958</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" ref="I6:I10" si="4">H6/D6</f>
+        <f t="shared" si="0"/>
         <v>6.3132134785052904E-2</v>
       </c>
     </row>
@@ -1548,7 +2094,7 @@
         <v>13229374.523517389</v>
       </c>
       <c r="D7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26458749.047034778</v>
       </c>
       <c r="E7" s="6">
@@ -1558,15 +2104,15 @@
         <v>169440</v>
       </c>
       <c r="G7" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>26628189.047034778</v>
       </c>
       <c r="H7" s="46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>169440</v>
       </c>
       <c r="I7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>6.403930877411949E-3</v>
       </c>
     </row>
@@ -1581,7 +2127,7 @@
         <v>740654.86782760639</v>
       </c>
       <c r="D8" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1481309.7356552128</v>
       </c>
       <c r="E8" s="6">
@@ -1591,15 +2137,15 @@
         <v>9600</v>
       </c>
       <c r="G8" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1490909.7356552128</v>
       </c>
       <c r="H8" s="46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9600</v>
       </c>
       <c r="I8" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>6.4807513033415184E-3</v>
       </c>
     </row>
@@ -1614,7 +2160,7 @@
         <v>4526723.9400540851</v>
       </c>
       <c r="D9" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9053447.8801081702</v>
       </c>
       <c r="E9" s="9">
@@ -1624,15 +2170,15 @@
         <v>52088.400000000009</v>
       </c>
       <c r="G9" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9105536.2801081706</v>
       </c>
       <c r="H9" s="47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>52088.400000000373</v>
       </c>
       <c r="I9" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>5.7534323596700292E-3</v>
       </c>
     </row>
@@ -1669,7 +2215,7 @@
         <v>42419359.919999994</v>
       </c>
       <c r="I10" s="49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>6.3825222786560998E-2</v>
       </c>
     </row>
@@ -1683,28 +2229,244 @@
       <c r="H11" s="7"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+    <row r="12" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="B12" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>52</v>
+      </c>
       <c r="H12" s="7"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H17" s="37"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H18" s="38"/>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="1">
+        <f>IFERROR(H14/D14,)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" ref="I15:I29" si="6">IFERROR(H15/D15,)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="37"/>
+      <c r="I18" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="38"/>
+      <c r="I19" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="51"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="11">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="53">
+        <f>SUM(B14:B28)</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="53">
+        <f t="shared" ref="C29:H29" si="7">SUM(C14:C28)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="53">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="53">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="53">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="53">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="53">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="49">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF701FE-00E5-43CD-84B1-B25BD0D56267}">
   <dimension ref="A1:BT25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Budgeting System_Manpower Report.xlsx
+++ b/Budgeting System_Manpower Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oclpholdings-my.sharepoint.com/personal/jumalonpvp_ortigas_com_ph/Documents/Documents/Budgeting System/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jumalonpvp\Downloads\Budgeting System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="465" documentId="8_{B440BBE7-9F96-47D5-8577-254065B29B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2C1DDFC-A472-40A7-AEEA-1EEB5FE00D9D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38603EF-68E4-4055-B3B1-B291AB23AF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{09E9E6D6-0F48-4124-9B86-4777CBE4DCA7}"/>
   </bookViews>
@@ -309,12 +309,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -432,7 +438,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -533,6 +539,7 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2299,7 +2306,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" s="54" t="s">
         <v>9</v>
       </c>
       <c r="I16" s="1">
@@ -2308,7 +2315,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="A17" s="54" t="s">
         <v>10</v>
       </c>
       <c r="I17" s="1">
@@ -2317,7 +2324,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" s="54" t="s">
         <v>11</v>
       </c>
       <c r="H18" s="37"/>
